--- a/ResourcesPK/ProductExclusionFile2.xlsx
+++ b/ResourcesPK/ProductExclusionFile2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Policy Code</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>PL000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20014766 </t>
   </si>
 </sst>
 </file>
@@ -365,16 +362,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,7 +388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -404,8 +401,8 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
+      <c r="E2" s="1">
+        <v>20014766</v>
       </c>
     </row>
   </sheetData>
